--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{BD1525A3-32F9-4C98-879C-186ABDEA6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDBC320C-F514-4B13-AACC-28188D58D444}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{BD1525A3-32F9-4C98-879C-186ABDEA6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3842BF06-F399-41CA-8BC8-2E0B1C9312D3}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -342,6 +342,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1263,8 +1267,12 @@
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
+      <c r="D30" s="5">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0</v>
+      </c>
       <c r="F30" s="4" t="s">
         <v>22</v>
       </c>
@@ -1279,8 +1287,12 @@
       <c r="C31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1</v>
+      </c>
       <c r="F31" s="4" t="s">
         <v>19</v>
       </c>
@@ -1295,8 +1307,12 @@
       <c r="C32" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+      <c r="D32" s="5">
+        <v>3</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0</v>
+      </c>
       <c r="F32" s="4" t="s">
         <v>20</v>
       </c>
@@ -1311,8 +1327,12 @@
       <c r="C33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
+      <c r="D33" s="5">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1</v>
+      </c>
       <c r="F33" s="4" t="s">
         <v>14</v>
       </c>
@@ -1327,8 +1347,12 @@
       <c r="C34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
+      <c r="D34" s="5">
+        <v>5</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1</v>
+      </c>
       <c r="F34" s="4" t="s">
         <v>32</v>
       </c>

--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{BD1525A3-32F9-4C98-879C-186ABDEA6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3842BF06-F399-41CA-8BC8-2E0B1C9312D3}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{BD1525A3-32F9-4C98-879C-186ABDEA6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35281F45-F9C0-4940-994C-098A7029857B}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
@@ -1367,8 +1367,12 @@
       <c r="C35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
+      <c r="D35" s="5">
+        <v>2</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1</v>
+      </c>
       <c r="F35" s="4" t="s">
         <v>30</v>
       </c>
@@ -1383,8 +1387,12 @@
       <c r="C36" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
+      <c r="D36" s="5">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0</v>
+      </c>
       <c r="F36" s="4" t="s">
         <v>26</v>
       </c>
@@ -1399,8 +1407,12 @@
       <c r="C37" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
+      <c r="D37" s="5">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5">
+        <v>4</v>
+      </c>
       <c r="F37" s="4" t="s">
         <v>29</v>
       </c>
@@ -1415,8 +1427,12 @@
       <c r="C38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
+      <c r="D38" s="5">
+        <v>4</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0</v>
+      </c>
       <c r="F38" s="4" t="s">
         <v>40</v>
       </c>

--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{BD1525A3-32F9-4C98-879C-186ABDEA6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35281F45-F9C0-4940-994C-098A7029857B}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{BD1525A3-32F9-4C98-879C-186ABDEA6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C0173C-3DA8-4F08-B2F8-04998B972787}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
+    <workbookView xWindow="19200" yWindow="2205" windowWidth="8655" windowHeight="11295" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1447,8 +1447,12 @@
       <c r="C39" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
+      <c r="D39" s="5">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0</v>
+      </c>
       <c r="F39" s="4" t="s">
         <v>42</v>
       </c>
@@ -1463,8 +1467,12 @@
       <c r="C40" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
+      <c r="D40" s="5">
+        <v>2</v>
+      </c>
+      <c r="E40" s="5">
+        <v>2</v>
+      </c>
       <c r="F40" s="4" t="s">
         <v>36</v>
       </c>
@@ -1479,8 +1487,12 @@
       <c r="C41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
+      <c r="D41" s="5">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5">
+        <v>3</v>
+      </c>
       <c r="F41" s="4" t="s">
         <v>39</v>
       </c>
@@ -1495,8 +1507,12 @@
       <c r="C42" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
+      <c r="D42" s="5">
+        <v>2</v>
+      </c>
+      <c r="E42" s="5">
+        <v>0</v>
+      </c>
       <c r="F42" s="4" t="s">
         <v>52</v>
       </c>

--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoo\OneDrive\Documents\Personal Projects\World Cup\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{BD1525A3-32F9-4C98-879C-186ABDEA6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C0173C-3DA8-4F08-B2F8-04998B972787}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A36D2AB-D972-40ED-8B35-25835ECA4ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19200" yWindow="2205" windowWidth="8655" windowHeight="11295" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
@@ -342,10 +342,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1527,8 +1523,12 @@
       <c r="C43" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
+      <c r="D43" s="5">
+        <v>3</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0</v>
+      </c>
       <c r="F43" s="4" t="s">
         <v>47</v>
       </c>
@@ -1543,8 +1543,12 @@
       <c r="C44" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
+      <c r="D44" s="5">
+        <v>3</v>
+      </c>
+      <c r="E44" s="5">
+        <v>2</v>
+      </c>
       <c r="F44" s="4" t="s">
         <v>46</v>
       </c>
@@ -1559,8 +1563,12 @@
       <c r="C45" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
+      <c r="D45" s="5">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5">
+        <v>2</v>
+      </c>
       <c r="F45" s="4" t="s">
         <v>51</v>
       </c>

--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoo\OneDrive\Documents\Personal Projects\World Cup\data\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A36D2AB-D972-40ED-8B35-25835ECA4ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9A36D2AB-D972-40ED-8B35-25835ECA4ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3247E6B-A888-4F06-A633-05D5B1972523}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="2205" windowWidth="8655" windowHeight="11295" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1583,8 +1583,12 @@
       <c r="C46" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
+      <c r="D46" s="5">
+        <v>5</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0</v>
+      </c>
       <c r="F46" s="4" t="s">
         <v>62</v>
       </c>
@@ -1599,8 +1603,12 @@
       <c r="C47" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
+      <c r="D47" s="5">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0</v>
+      </c>
       <c r="F47" s="4" t="s">
         <v>60</v>
       </c>

--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoo\OneDrive\Documents\Personal Projects\World Cup\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9A36D2AB-D972-40ED-8B35-25835ECA4ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3247E6B-A888-4F06-A633-05D5B1972523}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48001E4-E497-4CE3-A3C5-E5B6CCEFAB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
@@ -1623,8 +1623,12 @@
       <c r="C48" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
+      <c r="D48" s="5">
+        <v>0</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1</v>
+      </c>
       <c r="F48" s="4" t="s">
         <v>59</v>
       </c>
@@ -1639,8 +1643,12 @@
       <c r="C49" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
+      <c r="D49" s="5">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5">
+        <v>0</v>
+      </c>
       <c r="F49" s="4" t="s">
         <v>56</v>
       </c>
@@ -1655,8 +1663,12 @@
       <c r="C50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
+      <c r="D50" s="5">
+        <v>2</v>
+      </c>
+      <c r="E50" s="5">
+        <v>1</v>
+      </c>
       <c r="F50" s="4" t="s">
         <v>10</v>
       </c>
@@ -1671,8 +1683,12 @@
       <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
+      <c r="D51" s="5">
+        <v>3</v>
+      </c>
+      <c r="E51" s="5">
+        <v>1</v>
+      </c>
       <c r="F51" s="4" t="s">
         <v>15</v>
       </c>
@@ -1687,8 +1703,12 @@
       <c r="C52" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
+      <c r="D52" s="5">
+        <v>4</v>
+      </c>
+      <c r="E52" s="5">
+        <v>2</v>
+      </c>
       <c r="F52" s="4" t="s">
         <v>20</v>
       </c>
@@ -1703,8 +1723,12 @@
       <c r="C53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
+      <c r="D53" s="5">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5">
+        <v>3</v>
+      </c>
       <c r="F53" s="4" t="s">
         <v>18</v>
       </c>
@@ -1719,8 +1743,12 @@
       <c r="C54" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
+      <c r="D54" s="5">
+        <v>1</v>
+      </c>
+      <c r="E54" s="5">
+        <v>0</v>
+      </c>
       <c r="F54" s="4" t="s">
         <v>7</v>
       </c>
@@ -1735,8 +1763,12 @@
       <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
+      <c r="D55" s="5">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5">
+        <v>3</v>
+      </c>
       <c r="F55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1751,8 +1783,12 @@
       <c r="C56" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
+      <c r="D56" s="5">
+        <v>0</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2</v>
+      </c>
       <c r="F56" s="4" t="s">
         <v>30</v>
       </c>
@@ -1767,8 +1803,12 @@
       <c r="C57" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
+      <c r="D57" s="5">
+        <v>2</v>
+      </c>
+      <c r="E57" s="5">
+        <v>1</v>
+      </c>
       <c r="F57" s="4" t="s">
         <v>25</v>
       </c>

--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoo\OneDrive\Documents\Personal Projects\World Cup\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48001E4-E497-4CE3-A3C5-E5B6CCEFAB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBD566A-D112-4C72-8AEB-4A2BB68D7E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
@@ -1823,8 +1823,12 @@
       <c r="C58" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
+      <c r="D58" s="5">
+        <v>1</v>
+      </c>
+      <c r="E58" s="5">
+        <v>3</v>
+      </c>
       <c r="F58" s="4" t="s">
         <v>28</v>
       </c>
@@ -1839,8 +1843,12 @@
       <c r="C59" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
+      <c r="D59" s="5">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1</v>
+      </c>
       <c r="F59" s="4" t="s">
         <v>32</v>
       </c>
@@ -1855,8 +1863,12 @@
       <c r="C60" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
+      <c r="D60" s="5">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5">
+        <v>0</v>
+      </c>
       <c r="F60" s="4" t="s">
         <v>22</v>
       </c>
@@ -1871,8 +1883,12 @@
       <c r="C61" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
+      <c r="D61" s="5">
+        <v>3</v>
+      </c>
+      <c r="E61" s="5">
+        <v>2</v>
+      </c>
       <c r="F61" s="4" t="s">
         <v>13</v>
       </c>

--- a/data/results/results.xlsx
+++ b/data/results/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoo\OneDrive\Documents\Personal Projects\World Cup\data\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBD566A-D112-4C72-8AEB-4A2BB68D7E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{2CBD566A-D112-4C72-8AEB-4A2BB68D7E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C656EAB-FF25-43DC-9BEA-DB8BC5906D46}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403C7857-7215-46D2-96DC-8A3B2156FE81}"/>
   </bookViews>
@@ -1903,8 +1903,12 @@
       <c r="C62" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
+      <c r="D62" s="5">
+        <v>1</v>
+      </c>
+      <c r="E62" s="5">
+        <v>4</v>
+      </c>
       <c r="F62" s="4" t="s">
         <v>45</v>
       </c>
@@ -1919,8 +1923,12 @@
       <c r="C63" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
+      <c r="D63" s="5">
+        <v>5</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0</v>
+      </c>
       <c r="F63" s="4" t="s">
         <v>47</v>
       </c>
@@ -1935,8 +1943,12 @@
       <c r="C64" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
+      <c r="D64" s="5">
+        <v>0</v>
+      </c>
+      <c r="E64" s="5">
+        <v>0</v>
+      </c>
       <c r="F64" s="4" t="s">
         <v>40</v>
       </c>
@@ -1951,8 +1963,12 @@
       <c r="C65" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
+      <c r="D65" s="5">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5">
+        <v>1</v>
+      </c>
       <c r="F65" s="4" t="s">
         <v>35</v>
       </c>
@@ -1967,8 +1983,12 @@
       <c r="C66" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
+      <c r="D66" s="5">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5">
+        <v>1</v>
+      </c>
       <c r="F66" s="4" t="s">
         <v>42</v>
       </c>
@@ -1983,8 +2003,12 @@
       <c r="C67" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
+      <c r="D67" s="5">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5">
+        <v>5</v>
+      </c>
       <c r="F67" s="4" t="s">
         <v>38</v>
       </c>
@@ -1999,8 +2023,12 @@
       <c r="C68" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
+      <c r="D68" s="5">
+        <v>2</v>
+      </c>
+      <c r="E68" s="5">
+        <v>1</v>
+      </c>
       <c r="F68" s="4" t="s">
         <v>60</v>
       </c>
@@ -2015,8 +2043,12 @@
       <c r="C69" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
+      <c r="D69" s="5">
+        <v>0</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2</v>
+      </c>
       <c r="F69" s="4" t="s">
         <v>58</v>
       </c>
@@ -2031,8 +2063,12 @@
       <c r="C70" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
+      <c r="D70" s="5">
+        <v>0</v>
+      </c>
+      <c r="E70" s="5">
+        <v>0</v>
+      </c>
       <c r="F70" s="4" t="s">
         <v>55</v>
       </c>
@@ -2047,8 +2083,12 @@
       <c r="C71" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
+      <c r="D71" s="5">
+        <v>3</v>
+      </c>
+      <c r="E71" s="5">
+        <v>1</v>
+      </c>
       <c r="F71" s="4" t="s">
         <v>62</v>
       </c>
@@ -2063,8 +2103,12 @@
       <c r="C72" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
+      <c r="D72" s="5">
+        <v>3</v>
+      </c>
+      <c r="E72" s="5">
+        <v>3</v>
+      </c>
       <c r="F72" s="4" t="s">
         <v>52</v>
       </c>
@@ -2079,8 +2123,12 @@
       <c r="C73" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
+      <c r="D73" s="5">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5">
+        <v>3</v>
+      </c>
       <c r="F73" s="4" t="s">
         <v>50</v>
       </c>
